--- a/recruitment/HND_人員推移_稟議添付資料.xlsx
+++ b/recruitment/HND_人員推移_稟議添付資料.xlsx
@@ -19,12 +19,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0;[Red]&quot;▲&quot;#,##0;&quot;−&quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;+&quot;#,##0;[Red]&quot;▲&quot;#,##0;&quot;±0&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]&quot;▲&quot;#,##0;0"/>
+    <numFmt numFmtId="165" formatCode="&quot;+&quot;#,##0;[Red]&quot;▲&quot;#,##0;0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0&quot;名&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -151,6 +151,23 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -196,7 +213,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -379,11 +396,25 @@
         <color rgb="001F3864"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -515,7 +546,42 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -701,6 +767,13 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <dLbls>
+          <dLblPos val="t"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -829,6 +902,13 @@
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <dLblPos val="outEnd"/>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
         <gapWidth val="60"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -904,7 +984,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3096000"/>
+    <ext cx="8460000" cy="3024000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -923,10 +1003,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7560000" cy="3096000"/>
+    <ext cx="8460000" cy="3024000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1588,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1797,7 +1877,7 @@
       </c>
       <c r="N7" s="37" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1936,7 @@
       </c>
       <c r="N8" s="41" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1996,7 @@
       </c>
       <c r="N9" s="37" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2563,7 @@
       </c>
       <c r="N22" s="41" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2623,7 @@
       </c>
       <c r="N23" s="48" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2637,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="50" t="inlineStr">
         <is>
-          <t>1. 数値の単位は「名」。青字セルは実績入力値、黒字セルは計算式による自動算出。マイナスは「▲」で表示。</t>
+          <t>1. 数値の単位は「名」。青字セルは実績入力値、黒字セルは計算式による自動算出。マイナスは「▲」（赤字）で表示。</t>
         </is>
       </c>
     </row>
@@ -2585,14 +2665,22 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="50" t="inlineStr">
         <is>
-          <t>5. 出典：HND MMチーム 人員推移管理表（2025年9月〜2026年8月実績）。</t>
+          <t>5. 「年間計」欄の「—」は、月次の累計になじまない項目（在籍数・過不足）であることを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="50" t="inlineStr">
+        <is>
+          <t>6. 出典：HND MMチーム 人員推移管理表（2025年9月〜2026年8月実績）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A27:N27"/>
+    <mergeCell ref="A31:N31"/>
     <mergeCell ref="A6:N6"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A26:N26"/>
@@ -2625,16 +2713,29 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L4"/>
+  <dimension ref="B2:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="6.8" customWidth="1" min="3" max="3"/>
+    <col width="6.8" customWidth="1" min="4" max="4"/>
+    <col width="6.8" customWidth="1" min="5" max="5"/>
+    <col width="6.8" customWidth="1" min="6" max="6"/>
+    <col width="6.8" customWidth="1" min="7" max="7"/>
+    <col width="6.8" customWidth="1" min="8" max="8"/>
+    <col width="6.8" customWidth="1" min="9" max="9"/>
+    <col width="6.8" customWidth="1" min="10" max="10"/>
+    <col width="6.8" customWidth="1" min="11" max="11"/>
+    <col width="6.8" customWidth="1" min="12" max="12"/>
+    <col width="6.8" customWidth="1" min="13" max="13"/>
+    <col width="6.8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
@@ -2645,7 +2746,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="51" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>対象期間：2025年9月〜2026年8月　／　採用媒体の活用に関する稟議　添付資料　3/3</t>
         </is>
@@ -2663,14 +2764,835 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>月別数値：必要数・稼働数</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="D25" s="52" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="E25" s="52" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="G25" s="52" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="H25" s="52" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="I25" s="52" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="J25" s="52" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="K25" s="52" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="L25" s="52" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="M25" s="52" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="N25" s="52" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>必要数 (a)</t>
+        </is>
+      </c>
+      <c r="C26" s="54">
+        <f>'月次推移'!B7</f>
+        <v>20</v>
+      </c>
+      <c r="D26" s="54">
+        <f>'月次推移'!C7</f>
+        <v>25</v>
+      </c>
+      <c r="E26" s="54">
+        <f>'月次推移'!D7</f>
+        <v>25</v>
+      </c>
+      <c r="F26" s="54">
+        <f>'月次推移'!E7</f>
+        <v>25</v>
+      </c>
+      <c r="G26" s="54">
+        <f>'月次推移'!F7</f>
+        <v>25</v>
+      </c>
+      <c r="H26" s="54">
+        <f>'月次推移'!G7</f>
+        <v>25</v>
+      </c>
+      <c r="I26" s="54">
+        <f>'月次推移'!H7</f>
+        <v>25</v>
+      </c>
+      <c r="J26" s="54">
+        <f>'月次推移'!I7</f>
+        <v>25</v>
+      </c>
+      <c r="K26" s="54">
+        <f>'月次推移'!J7</f>
+        <v>25</v>
+      </c>
+      <c r="L26" s="54">
+        <f>'月次推移'!K7</f>
+        <v>25</v>
+      </c>
+      <c r="M26" s="54">
+        <f>'月次推移'!L7</f>
+        <v>25</v>
+      </c>
+      <c r="N26" s="55">
+        <f>'月次推移'!M7</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="53" t="inlineStr">
+        <is>
+          <t>月初稼働数 (b)</t>
+        </is>
+      </c>
+      <c r="C27" s="54">
+        <f>'月次推移'!B8</f>
+        <v>20</v>
+      </c>
+      <c r="D27" s="54">
+        <f>'月次推移'!C8</f>
+        <v>19</v>
+      </c>
+      <c r="E27" s="54">
+        <f>'月次推移'!D8</f>
+        <v>22</v>
+      </c>
+      <c r="F27" s="54">
+        <f>'月次推移'!E8</f>
+        <v>27</v>
+      </c>
+      <c r="G27" s="54">
+        <f>'月次推移'!F8</f>
+        <v>29</v>
+      </c>
+      <c r="H27" s="54">
+        <f>'月次推移'!G8</f>
+        <v>27</v>
+      </c>
+      <c r="I27" s="54">
+        <f>'月次推移'!H8</f>
+        <v>27</v>
+      </c>
+      <c r="J27" s="54">
+        <f>'月次推移'!I8</f>
+        <v>26</v>
+      </c>
+      <c r="K27" s="54">
+        <f>'月次推移'!J8</f>
+        <v>26</v>
+      </c>
+      <c r="L27" s="54">
+        <f>'月次推移'!K8</f>
+        <v>26</v>
+      </c>
+      <c r="M27" s="54">
+        <f>'月次推移'!L8</f>
+        <v>25</v>
+      </c>
+      <c r="N27" s="55">
+        <f>'月次推移'!M8</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="56" t="inlineStr">
+        <is>
+          <t>月末稼働数 (c)</t>
+        </is>
+      </c>
+      <c r="C28" s="57">
+        <f>'月次推移'!B22</f>
+        <v>19</v>
+      </c>
+      <c r="D28" s="57">
+        <f>'月次推移'!C22</f>
+        <v>22</v>
+      </c>
+      <c r="E28" s="57">
+        <f>'月次推移'!D22</f>
+        <v>27</v>
+      </c>
+      <c r="F28" s="57">
+        <f>'月次推移'!E22</f>
+        <v>29</v>
+      </c>
+      <c r="G28" s="57">
+        <f>'月次推移'!F22</f>
+        <v>27</v>
+      </c>
+      <c r="H28" s="57">
+        <f>'月次推移'!G22</f>
+        <v>27</v>
+      </c>
+      <c r="I28" s="57">
+        <f>'月次推移'!H22</f>
+        <v>26</v>
+      </c>
+      <c r="J28" s="57">
+        <f>'月次推移'!I22</f>
+        <v>26</v>
+      </c>
+      <c r="K28" s="57">
+        <f>'月次推移'!J22</f>
+        <v>26</v>
+      </c>
+      <c r="L28" s="57">
+        <f>'月次推移'!K22</f>
+        <v>25</v>
+      </c>
+      <c r="M28" s="57">
+        <f>'月次推移'!L22</f>
+        <v>23</v>
+      </c>
+      <c r="N28" s="58">
+        <f>'月次推移'!M22</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="59" t="inlineStr">
+        <is>
+          <t>過不足 (c − a)</t>
+        </is>
+      </c>
+      <c r="C29" s="60">
+        <f>'月次推移'!B23</f>
+        <v>-1</v>
+      </c>
+      <c r="D29" s="60">
+        <f>'月次推移'!C23</f>
+        <v>-3</v>
+      </c>
+      <c r="E29" s="60">
+        <f>'月次推移'!D23</f>
+        <v>2</v>
+      </c>
+      <c r="F29" s="60">
+        <f>'月次推移'!E23</f>
+        <v>4</v>
+      </c>
+      <c r="G29" s="60">
+        <f>'月次推移'!F23</f>
+        <v>2</v>
+      </c>
+      <c r="H29" s="60">
+        <f>'月次推移'!G23</f>
+        <v>2</v>
+      </c>
+      <c r="I29" s="60">
+        <f>'月次推移'!H23</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="60">
+        <f>'月次推移'!I23</f>
+        <v>1</v>
+      </c>
+      <c r="K29" s="60">
+        <f>'月次推移'!J23</f>
+        <v>1</v>
+      </c>
+      <c r="L29" s="60">
+        <f>'月次推移'!K23</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="60">
+        <f>'月次推移'!L23</f>
+        <v>-2</v>
+      </c>
+      <c r="N29" s="61">
+        <f>'月次推移'!M23</f>
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>月別数値：入（増員）・出（減員）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="B51" s="52" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="E51" s="52" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="F51" s="52" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="G51" s="52" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="H51" s="52" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="I51" s="52" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="J51" s="52" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="K51" s="52" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="L51" s="52" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="M51" s="52" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="N51" s="52" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="53" t="inlineStr">
+        <is>
+          <t>採用数（正社員）</t>
+        </is>
+      </c>
+      <c r="C52" s="54">
+        <f>'月次推移'!B11</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="54">
+        <f>'月次推移'!C11</f>
+        <v>4</v>
+      </c>
+      <c r="E52" s="54">
+        <f>'月次推移'!D11</f>
+        <v>6</v>
+      </c>
+      <c r="F52" s="54">
+        <f>'月次推移'!E11</f>
+        <v>4</v>
+      </c>
+      <c r="G52" s="54">
+        <f>'月次推移'!F11</f>
+        <v>1</v>
+      </c>
+      <c r="H52" s="54">
+        <f>'月次推移'!G11</f>
+        <v>3</v>
+      </c>
+      <c r="I52" s="54">
+        <f>'月次推移'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="54">
+        <f>'月次推移'!I11</f>
+        <v>3</v>
+      </c>
+      <c r="K52" s="54">
+        <f>'月次推移'!J11</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="54">
+        <f>'月次推移'!K11</f>
+        <v>0</v>
+      </c>
+      <c r="M52" s="54">
+        <f>'月次推移'!L11</f>
+        <v>0</v>
+      </c>
+      <c r="N52" s="55">
+        <f>'月次推移'!M11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="53" t="inlineStr">
+        <is>
+          <t>採用数（派遣）</t>
+        </is>
+      </c>
+      <c r="C53" s="54">
+        <f>'月次推移'!B12</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="54">
+        <f>'月次推移'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="54">
+        <f>'月次推移'!D12</f>
+        <v>1</v>
+      </c>
+      <c r="F53" s="54">
+        <f>'月次推移'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="54">
+        <f>'月次推移'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="54">
+        <f>'月次推移'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="54">
+        <f>'月次推移'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="54">
+        <f>'月次推移'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="54">
+        <f>'月次推移'!J12</f>
+        <v>0</v>
+      </c>
+      <c r="L53" s="54">
+        <f>'月次推移'!K12</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="54">
+        <f>'月次推移'!L12</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="55">
+        <f>'月次推移'!M12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="56" t="inlineStr">
+        <is>
+          <t>入 合計</t>
+        </is>
+      </c>
+      <c r="C54" s="57">
+        <f>'月次推移'!B14</f>
+        <v>1</v>
+      </c>
+      <c r="D54" s="57">
+        <f>'月次推移'!C14</f>
+        <v>4</v>
+      </c>
+      <c r="E54" s="57">
+        <f>'月次推移'!D14</f>
+        <v>7</v>
+      </c>
+      <c r="F54" s="57">
+        <f>'月次推移'!E14</f>
+        <v>4</v>
+      </c>
+      <c r="G54" s="57">
+        <f>'月次推移'!F14</f>
+        <v>1</v>
+      </c>
+      <c r="H54" s="57">
+        <f>'月次推移'!G14</f>
+        <v>3</v>
+      </c>
+      <c r="I54" s="57">
+        <f>'月次推移'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="57">
+        <f>'月次推移'!I14</f>
+        <v>3</v>
+      </c>
+      <c r="K54" s="57">
+        <f>'月次推移'!J14</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="57">
+        <f>'月次推移'!K14</f>
+        <v>0</v>
+      </c>
+      <c r="M54" s="57">
+        <f>'月次推移'!L14</f>
+        <v>0</v>
+      </c>
+      <c r="N54" s="58">
+        <f>'月次推移'!M14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="53" t="inlineStr">
+        <is>
+          <t>退職数（正社員）</t>
+        </is>
+      </c>
+      <c r="C55" s="54">
+        <f>'月次推移'!B16</f>
+        <v>2</v>
+      </c>
+      <c r="D55" s="54">
+        <f>'月次推移'!C16</f>
+        <v>1</v>
+      </c>
+      <c r="E55" s="54">
+        <f>'月次推移'!D16</f>
+        <v>1</v>
+      </c>
+      <c r="F55" s="54">
+        <f>'月次推移'!E16</f>
+        <v>1</v>
+      </c>
+      <c r="G55" s="54">
+        <f>'月次推移'!F16</f>
+        <v>3</v>
+      </c>
+      <c r="H55" s="54">
+        <f>'月次推移'!G16</f>
+        <v>3</v>
+      </c>
+      <c r="I55" s="54">
+        <f>'月次推移'!H16</f>
+        <v>1</v>
+      </c>
+      <c r="J55" s="54">
+        <f>'月次推移'!I16</f>
+        <v>1</v>
+      </c>
+      <c r="K55" s="54">
+        <f>'月次推移'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="L55" s="54">
+        <f>'月次推移'!K16</f>
+        <v>1</v>
+      </c>
+      <c r="M55" s="54">
+        <f>'月次推移'!L16</f>
+        <v>2</v>
+      </c>
+      <c r="N55" s="55">
+        <f>'月次推移'!M16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>退職数（派遣）</t>
+        </is>
+      </c>
+      <c r="C56" s="54">
+        <f>'月次推移'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="54">
+        <f>'月次推移'!C17</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="54">
+        <f>'月次推移'!D17</f>
+        <v>1</v>
+      </c>
+      <c r="F56" s="54">
+        <f>'月次推移'!E17</f>
+        <v>1</v>
+      </c>
+      <c r="G56" s="54">
+        <f>'月次推移'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="54">
+        <f>'月次推移'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="54">
+        <f>'月次推移'!H17</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="54">
+        <f>'月次推移'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="54">
+        <f>'月次推移'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="54">
+        <f>'月次推移'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="54">
+        <f>'月次推移'!L17</f>
+        <v>0</v>
+      </c>
+      <c r="N56" s="55">
+        <f>'月次推移'!M17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="53" t="inlineStr">
+        <is>
+          <t>長期欠勤等による離脱</t>
+        </is>
+      </c>
+      <c r="C57" s="54">
+        <f>'月次推移'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="54">
+        <f>'月次推移'!C18</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="54">
+        <f>'月次推移'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="54">
+        <f>'月次推移'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="54">
+        <f>'月次推移'!F18</f>
+        <v>0</v>
+      </c>
+      <c r="H57" s="54">
+        <f>'月次推移'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="I57" s="54">
+        <f>'月次推移'!H18</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="54">
+        <f>'月次推移'!I18</f>
+        <v>2</v>
+      </c>
+      <c r="K57" s="54">
+        <f>'月次推移'!J18</f>
+        <v>0</v>
+      </c>
+      <c r="L57" s="54">
+        <f>'月次推移'!K18</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="54">
+        <f>'月次推移'!L18</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="55">
+        <f>'月次推移'!M18</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="56" t="inlineStr">
+        <is>
+          <t>出 合計</t>
+        </is>
+      </c>
+      <c r="C58" s="57">
+        <f>'月次推移'!B20</f>
+        <v>2</v>
+      </c>
+      <c r="D58" s="57">
+        <f>'月次推移'!C20</f>
+        <v>1</v>
+      </c>
+      <c r="E58" s="57">
+        <f>'月次推移'!D20</f>
+        <v>2</v>
+      </c>
+      <c r="F58" s="57">
+        <f>'月次推移'!E20</f>
+        <v>2</v>
+      </c>
+      <c r="G58" s="57">
+        <f>'月次推移'!F20</f>
+        <v>3</v>
+      </c>
+      <c r="H58" s="57">
+        <f>'月次推移'!G20</f>
+        <v>3</v>
+      </c>
+      <c r="I58" s="57">
+        <f>'月次推移'!H20</f>
+        <v>1</v>
+      </c>
+      <c r="J58" s="57">
+        <f>'月次推移'!I20</f>
+        <v>3</v>
+      </c>
+      <c r="K58" s="57">
+        <f>'月次推移'!J20</f>
+        <v>0</v>
+      </c>
+      <c r="L58" s="57">
+        <f>'月次推移'!K20</f>
+        <v>1</v>
+      </c>
+      <c r="M58" s="57">
+        <f>'月次推移'!L20</f>
+        <v>2</v>
+      </c>
+      <c r="N58" s="58">
+        <f>'月次推移'!M20</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="59" t="inlineStr">
+        <is>
+          <t>純増減（入 − 出）</t>
+        </is>
+      </c>
+      <c r="C59" s="60">
+        <f>'月次推移'!B14-'月次推移'!B20</f>
+        <v>-1</v>
+      </c>
+      <c r="D59" s="60">
+        <f>'月次推移'!C14-'月次推移'!C20</f>
+        <v>3</v>
+      </c>
+      <c r="E59" s="60">
+        <f>'月次推移'!D14-'月次推移'!D20</f>
+        <v>5</v>
+      </c>
+      <c r="F59" s="60">
+        <f>'月次推移'!E14-'月次推移'!E20</f>
+        <v>2</v>
+      </c>
+      <c r="G59" s="60">
+        <f>'月次推移'!F14-'月次推移'!F20</f>
+        <v>-2</v>
+      </c>
+      <c r="H59" s="60">
+        <f>'月次推移'!G14-'月次推移'!G20</f>
+        <v>0</v>
+      </c>
+      <c r="I59" s="60">
+        <f>'月次推移'!H14-'月次推移'!H20</f>
+        <v>-1</v>
+      </c>
+      <c r="J59" s="60">
+        <f>'月次推移'!I14-'月次推移'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="K59" s="60">
+        <f>'月次推移'!J14-'月次推移'!J20</f>
+        <v>0</v>
+      </c>
+      <c r="L59" s="60">
+        <f>'月次推移'!K14-'月次推移'!K20</f>
+        <v>-1</v>
+      </c>
+      <c r="M59" s="60">
+        <f>'月次推移'!L14-'月次推移'!L20</f>
+        <v>-2</v>
+      </c>
+      <c r="N59" s="61">
+        <f>'月次推移'!M14-'月次推移'!M20</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="62" t="inlineStr">
+        <is>
+          <t>※ 数値はいずれも「月次推移」シートを参照。単位は名、マイナスは「▲」（赤字）で表示。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B61:N61"/>
+    <mergeCell ref="B24:N24"/>
+    <mergeCell ref="B50:N50"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B2:N2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/recruitment/HND_人員推移_稟議添付資料.xlsx
+++ b/recruitment/HND_人員推移_稟議添付資料.xlsx
@@ -7,24 +7,28 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="月次推移" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="グラフ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="A4一枚" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="サマリー" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="月次推移" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="グラフ" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'A4一枚'!$A$1:$P$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]&quot;▲&quot;#,##0;0"/>
     <numFmt numFmtId="165" formatCode="&quot;+&quot;#,##0;[Red]&quot;▲&quot;#,##0;0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0&quot;名&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot;名 ／ 年&quot;"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,6 +172,63 @@
       <color rgb="00000000"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00808080"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="001F1F1F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -213,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -410,19 +471,166 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+    </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F3864"/>
+      </left>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="001F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="27" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="27" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="29" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="34" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -586,7 +794,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="游ゴシック"/>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE0E0"/>
+          <bgColor rgb="00FCE0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="游ゴシック"/>
@@ -675,6 +897,119 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'月次推移'!A7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月次推移'!$B$5:$M$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月次推移'!$B$7:$M$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'月次推移'!A22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'月次推移'!$B$5:$M$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'月次推移'!$B$22:$M$22</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -825,7 +1160,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -976,6 +1311,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8856000" cy="1404000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1314,6 +1676,1088 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="1.2" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="7.6" customWidth="1" min="3" max="3"/>
+    <col width="7.6" customWidth="1" min="4" max="4"/>
+    <col width="7.6" customWidth="1" min="5" max="5"/>
+    <col width="7.6" customWidth="1" min="6" max="6"/>
+    <col width="7.6" customWidth="1" min="7" max="7"/>
+    <col width="7.6" customWidth="1" min="8" max="8"/>
+    <col width="7.6" customWidth="1" min="9" max="9"/>
+    <col width="7.6" customWidth="1" min="10" max="10"/>
+    <col width="7.6" customWidth="1" min="11" max="11"/>
+    <col width="7.6" customWidth="1" min="12" max="12"/>
+    <col width="7.6" customWidth="1" min="13" max="13"/>
+    <col width="7.6" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="1.2" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>HND MMチーム　人員体制の現状と採用課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>対象期間：2025年9月〜2026年8月（12ヶ月実績）　／　採用媒体の活用に関する稟議　添付資料　／　単位：名</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>年間退職者数</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>年間離職率</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>月平均退職者数</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>年間の純増減</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="9" t="n"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>期末の過不足</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="23" customHeight="1">
+      <c r="B5" s="10">
+        <f>'月次推移'!N16+'月次推移'!N17</f>
+        <v>19</v>
+      </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="12">
+        <f>('月次推移'!N16+'月次推移'!N17)/AVERAGE('月次推移'!B8:M8)</f>
+        <v>0.7676767677</v>
+      </c>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="14">
+        <f>('月次推移'!N16+'月次推移'!N17)/12</f>
+        <v>1.5833333333</v>
+      </c>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="15">
+        <f>'月次推移'!N14-'月次推移'!N20</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="16">
+        <f>'月次推移'!M23</f>
+        <v>-5</v>
+      </c>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="13" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>正社員17名・派遣2名</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>退職者数 ÷ 平均月初稼働数</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="18" t="n"/>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>12ヶ月中11ヶ月で退職が発生</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="18" t="n"/>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>採用23名 − 離脱23名</t>
+        </is>
+      </c>
+      <c r="K6" s="19" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>2026年8月末　必要数25名</t>
+        </is>
+      </c>
+      <c r="N6" s="19" t="n"/>
+      <c r="O6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="5" customHeight="1"/>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>月次推移（2025年9月〜2026年8月）</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="21" t="n"/>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="21" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>項　目</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
+      <c r="M9" s="22" t="n"/>
+      <c r="N9" s="22" t="n"/>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t>年間計</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>必要数 (a)</t>
+        </is>
+      </c>
+      <c r="C11" s="25">
+        <f>'月次推移'!B7</f>
+        <v>20</v>
+      </c>
+      <c r="D11" s="25">
+        <f>'月次推移'!C7</f>
+        <v>25</v>
+      </c>
+      <c r="E11" s="25">
+        <f>'月次推移'!D7</f>
+        <v>25</v>
+      </c>
+      <c r="F11" s="25">
+        <f>'月次推移'!E7</f>
+        <v>25</v>
+      </c>
+      <c r="G11" s="25">
+        <f>'月次推移'!F7</f>
+        <v>25</v>
+      </c>
+      <c r="H11" s="25">
+        <f>'月次推移'!G7</f>
+        <v>25</v>
+      </c>
+      <c r="I11" s="25">
+        <f>'月次推移'!H7</f>
+        <v>25</v>
+      </c>
+      <c r="J11" s="25">
+        <f>'月次推移'!I7</f>
+        <v>25</v>
+      </c>
+      <c r="K11" s="25">
+        <f>'月次推移'!J7</f>
+        <v>25</v>
+      </c>
+      <c r="L11" s="25">
+        <f>'月次推移'!K7</f>
+        <v>25</v>
+      </c>
+      <c r="M11" s="25">
+        <f>'月次推移'!L7</f>
+        <v>25</v>
+      </c>
+      <c r="N11" s="25">
+        <f>'月次推移'!M7</f>
+        <v>25</v>
+      </c>
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>月初稼働数 (b)</t>
+        </is>
+      </c>
+      <c r="C12" s="25">
+        <f>'月次推移'!B8</f>
+        <v>20</v>
+      </c>
+      <c r="D12" s="25">
+        <f>'月次推移'!C8</f>
+        <v>19</v>
+      </c>
+      <c r="E12" s="25">
+        <f>'月次推移'!D8</f>
+        <v>22</v>
+      </c>
+      <c r="F12" s="25">
+        <f>'月次推移'!E8</f>
+        <v>27</v>
+      </c>
+      <c r="G12" s="25">
+        <f>'月次推移'!F8</f>
+        <v>29</v>
+      </c>
+      <c r="H12" s="25">
+        <f>'月次推移'!G8</f>
+        <v>27</v>
+      </c>
+      <c r="I12" s="25">
+        <f>'月次推移'!H8</f>
+        <v>27</v>
+      </c>
+      <c r="J12" s="25">
+        <f>'月次推移'!I8</f>
+        <v>26</v>
+      </c>
+      <c r="K12" s="25">
+        <f>'月次推移'!J8</f>
+        <v>26</v>
+      </c>
+      <c r="L12" s="25">
+        <f>'月次推移'!K8</f>
+        <v>26</v>
+      </c>
+      <c r="M12" s="25">
+        <f>'月次推移'!L8</f>
+        <v>25</v>
+      </c>
+      <c r="N12" s="25">
+        <f>'月次推移'!M8</f>
+        <v>23</v>
+      </c>
+      <c r="O12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>採用数（正社員）</t>
+        </is>
+      </c>
+      <c r="C13" s="25">
+        <f>'月次推移'!B11</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="25">
+        <f>'月次推移'!C11</f>
+        <v>4</v>
+      </c>
+      <c r="E13" s="25">
+        <f>'月次推移'!D11</f>
+        <v>6</v>
+      </c>
+      <c r="F13" s="25">
+        <f>'月次推移'!E11</f>
+        <v>4</v>
+      </c>
+      <c r="G13" s="25">
+        <f>'月次推移'!F11</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="25">
+        <f>'月次推移'!G11</f>
+        <v>3</v>
+      </c>
+      <c r="I13" s="25">
+        <f>'月次推移'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="25">
+        <f>'月次推移'!I11</f>
+        <v>3</v>
+      </c>
+      <c r="K13" s="25">
+        <f>'月次推移'!J11</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="25">
+        <f>'月次推移'!K11</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="25">
+        <f>'月次推移'!L11</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="25">
+        <f>'月次推移'!M11</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="27">
+        <f>'月次推移'!N11</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>採用数（派遣）</t>
+        </is>
+      </c>
+      <c r="C14" s="25">
+        <f>'月次推移'!B12</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="25">
+        <f>'月次推移'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="25">
+        <f>'月次推移'!D12</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="25">
+        <f>'月次推移'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="25">
+        <f>'月次推移'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="25">
+        <f>'月次推移'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="25">
+        <f>'月次推移'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="25">
+        <f>'月次推移'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="25">
+        <f>'月次推移'!J12</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="25">
+        <f>'月次推移'!K12</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="25">
+        <f>'月次推移'!L12</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="25">
+        <f>'月次推移'!M12</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="27">
+        <f>'月次推移'!N12</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>入 合計</t>
+        </is>
+      </c>
+      <c r="C15" s="29">
+        <f>'月次推移'!B14</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="29">
+        <f>'月次推移'!C14</f>
+        <v>4</v>
+      </c>
+      <c r="E15" s="29">
+        <f>'月次推移'!D14</f>
+        <v>7</v>
+      </c>
+      <c r="F15" s="29">
+        <f>'月次推移'!E14</f>
+        <v>4</v>
+      </c>
+      <c r="G15" s="29">
+        <f>'月次推移'!F14</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="29">
+        <f>'月次推移'!G14</f>
+        <v>3</v>
+      </c>
+      <c r="I15" s="29">
+        <f>'月次推移'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="29">
+        <f>'月次推移'!I14</f>
+        <v>3</v>
+      </c>
+      <c r="K15" s="29">
+        <f>'月次推移'!J14</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="29">
+        <f>'月次推移'!K14</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="29">
+        <f>'月次推移'!L14</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
+        <f>'月次推移'!M14</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="27">
+        <f>'月次推移'!N14</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>退職数（正社員）</t>
+        </is>
+      </c>
+      <c r="C16" s="25">
+        <f>'月次推移'!B16</f>
+        <v>2</v>
+      </c>
+      <c r="D16" s="25">
+        <f>'月次推移'!C16</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="25">
+        <f>'月次推移'!D16</f>
+        <v>1</v>
+      </c>
+      <c r="F16" s="25">
+        <f>'月次推移'!E16</f>
+        <v>1</v>
+      </c>
+      <c r="G16" s="25">
+        <f>'月次推移'!F16</f>
+        <v>3</v>
+      </c>
+      <c r="H16" s="25">
+        <f>'月次推移'!G16</f>
+        <v>3</v>
+      </c>
+      <c r="I16" s="25">
+        <f>'月次推移'!H16</f>
+        <v>1</v>
+      </c>
+      <c r="J16" s="25">
+        <f>'月次推移'!I16</f>
+        <v>1</v>
+      </c>
+      <c r="K16" s="25">
+        <f>'月次推移'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="25">
+        <f>'月次推移'!K16</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="25">
+        <f>'月次推移'!L16</f>
+        <v>2</v>
+      </c>
+      <c r="N16" s="25">
+        <f>'月次推移'!M16</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="27">
+        <f>'月次推移'!N16</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>退職数（派遣）</t>
+        </is>
+      </c>
+      <c r="C17" s="25">
+        <f>'月次推移'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="25">
+        <f>'月次推移'!C17</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="25">
+        <f>'月次推移'!D17</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="25">
+        <f>'月次推移'!E17</f>
+        <v>1</v>
+      </c>
+      <c r="G17" s="25">
+        <f>'月次推移'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="25">
+        <f>'月次推移'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="25">
+        <f>'月次推移'!H17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="25">
+        <f>'月次推移'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="25">
+        <f>'月次推移'!J17</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="25">
+        <f>'月次推移'!K17</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="25">
+        <f>'月次推移'!L17</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="25">
+        <f>'月次推移'!M17</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="27">
+        <f>'月次推移'!N17</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>長期欠勤等による離脱者数</t>
+        </is>
+      </c>
+      <c r="C18" s="25">
+        <f>'月次推移'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="25">
+        <f>'月次推移'!C18</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="25">
+        <f>'月次推移'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="25">
+        <f>'月次推移'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="25">
+        <f>'月次推移'!F18</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="25">
+        <f>'月次推移'!G18</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="25">
+        <f>'月次推移'!H18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="25">
+        <f>'月次推移'!I18</f>
+        <v>2</v>
+      </c>
+      <c r="K18" s="25">
+        <f>'月次推移'!J18</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="25">
+        <f>'月次推移'!K18</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="25">
+        <f>'月次推移'!L18</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <f>'月次推移'!M18</f>
+        <v>2</v>
+      </c>
+      <c r="O18" s="27">
+        <f>'月次推移'!N18</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>出 合計</t>
+        </is>
+      </c>
+      <c r="C19" s="29">
+        <f>'月次推移'!B20</f>
+        <v>2</v>
+      </c>
+      <c r="D19" s="29">
+        <f>'月次推移'!C20</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="29">
+        <f>'月次推移'!D20</f>
+        <v>2</v>
+      </c>
+      <c r="F19" s="29">
+        <f>'月次推移'!E20</f>
+        <v>2</v>
+      </c>
+      <c r="G19" s="29">
+        <f>'月次推移'!F20</f>
+        <v>3</v>
+      </c>
+      <c r="H19" s="29">
+        <f>'月次推移'!G20</f>
+        <v>3</v>
+      </c>
+      <c r="I19" s="29">
+        <f>'月次推移'!H20</f>
+        <v>1</v>
+      </c>
+      <c r="J19" s="29">
+        <f>'月次推移'!I20</f>
+        <v>3</v>
+      </c>
+      <c r="K19" s="29">
+        <f>'月次推移'!J20</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="29">
+        <f>'月次推移'!K20</f>
+        <v>1</v>
+      </c>
+      <c r="M19" s="29">
+        <f>'月次推移'!L20</f>
+        <v>2</v>
+      </c>
+      <c r="N19" s="29">
+        <f>'月次推移'!M20</f>
+        <v>3</v>
+      </c>
+      <c r="O19" s="27">
+        <f>'月次推移'!N20</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>月末稼働数 (c)</t>
+        </is>
+      </c>
+      <c r="C20" s="29">
+        <f>'月次推移'!B22</f>
+        <v>19</v>
+      </c>
+      <c r="D20" s="29">
+        <f>'月次推移'!C22</f>
+        <v>22</v>
+      </c>
+      <c r="E20" s="29">
+        <f>'月次推移'!D22</f>
+        <v>27</v>
+      </c>
+      <c r="F20" s="29">
+        <f>'月次推移'!E22</f>
+        <v>29</v>
+      </c>
+      <c r="G20" s="29">
+        <f>'月次推移'!F22</f>
+        <v>27</v>
+      </c>
+      <c r="H20" s="29">
+        <f>'月次推移'!G22</f>
+        <v>27</v>
+      </c>
+      <c r="I20" s="29">
+        <f>'月次推移'!H22</f>
+        <v>26</v>
+      </c>
+      <c r="J20" s="29">
+        <f>'月次推移'!I22</f>
+        <v>26</v>
+      </c>
+      <c r="K20" s="29">
+        <f>'月次推移'!J22</f>
+        <v>26</v>
+      </c>
+      <c r="L20" s="29">
+        <f>'月次推移'!K22</f>
+        <v>25</v>
+      </c>
+      <c r="M20" s="29">
+        <f>'月次推移'!L22</f>
+        <v>23</v>
+      </c>
+      <c r="N20" s="29">
+        <f>'月次推移'!M22</f>
+        <v>20</v>
+      </c>
+      <c r="O20" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>過不足 (c − a)</t>
+        </is>
+      </c>
+      <c r="C21" s="31">
+        <f>'月次推移'!B23</f>
+        <v>-1</v>
+      </c>
+      <c r="D21" s="31">
+        <f>'月次推移'!C23</f>
+        <v>-3</v>
+      </c>
+      <c r="E21" s="31">
+        <f>'月次推移'!D23</f>
+        <v>2</v>
+      </c>
+      <c r="F21" s="31">
+        <f>'月次推移'!E23</f>
+        <v>4</v>
+      </c>
+      <c r="G21" s="31">
+        <f>'月次推移'!F23</f>
+        <v>2</v>
+      </c>
+      <c r="H21" s="31">
+        <f>'月次推移'!G23</f>
+        <v>2</v>
+      </c>
+      <c r="I21" s="31">
+        <f>'月次推移'!H23</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="31">
+        <f>'月次推移'!I23</f>
+        <v>1</v>
+      </c>
+      <c r="K21" s="31">
+        <f>'月次推移'!J23</f>
+        <v>1</v>
+      </c>
+      <c r="L21" s="31">
+        <f>'月次推移'!K23</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="31">
+        <f>'月次推移'!L23</f>
+        <v>-2</v>
+      </c>
+      <c r="N21" s="31">
+        <f>'月次推移'!M23</f>
+        <v>-5</v>
+      </c>
+      <c r="O21" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="5" customHeight="1"/>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>必要数と稼働数の推移</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="21" t="n"/>
+    </row>
+    <row r="24" ht="14" customHeight="1"/>
+    <row r="25" ht="14" customHeight="1"/>
+    <row r="26" ht="14" customHeight="1"/>
+    <row r="27" ht="14" customHeight="1"/>
+    <row r="28" ht="14" customHeight="1"/>
+    <row r="29" ht="14" customHeight="1"/>
+    <row r="30" ht="14" customHeight="1"/>
+    <row r="31" ht="14" customHeight="1"/>
+    <row r="32" ht="5" customHeight="1"/>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>現状の課題</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="21" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="21" t="n"/>
+      <c r="L33" s="21" t="n"/>
+      <c r="M33" s="21" t="n"/>
+      <c r="N33" s="21" t="n"/>
+      <c r="O33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="13" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>1.　12ヶ月で19名（正社員17名・派遣2名）が退職。年間離職率76.8%、月平均1.6名のペースで欠員が発生している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>2.　年間23名を採用したが、同期間に23名（退職19名＋長期欠勤等による離脱4名）が離脱し、純増はゼロ。採用は欠員補充に費やされている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>3.　必要数が20名→25名へ増える一方、稼働数は期首・期末とも20名で横ばい。2026年8月末は稼働率80%（20名／25名）、▲5名の欠員となっている。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>今後1年間に必要となる採用数　＝　現時点の欠員 5名　＋　想定退職者数 19名</t>
+        </is>
+      </c>
+      <c r="C37" s="35" t="n"/>
+      <c r="D37" s="35" t="n"/>
+      <c r="E37" s="35" t="n"/>
+      <c r="F37" s="35" t="n"/>
+      <c r="G37" s="35" t="n"/>
+      <c r="H37" s="35" t="n"/>
+      <c r="I37" s="35" t="n"/>
+      <c r="J37" s="36">
+        <f>-'月次推移'!M23+'月次推移'!N16+'月次推移'!N17</f>
+        <v>24</v>
+      </c>
+      <c r="K37" s="35" t="n"/>
+      <c r="L37" s="35" t="n"/>
+      <c r="M37" s="35" t="n"/>
+      <c r="N37" s="35" t="n"/>
+      <c r="O37" s="37" t="n"/>
+    </row>
+    <row r="38" ht="11" customHeight="1">
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>※ 想定退職者数は直近12ヶ月の実績（19名）と同水準で推移すると仮定した試算値。異動（入）（出）は期間中いずれも0名のため本表では省略。明細は「月次推移」シート参照。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="B35:O35"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B23:O23"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="B8:O8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="J37:O37"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B36:O36"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C20:O20">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:O21">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1330,14 +2774,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="34" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>HND MMチーム　人員体制の現状と採用課題</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>対象期間：2025年9月〜2026年8月（12ヶ月実績）　／　採用媒体の活用に関する稟議　添付資料　1/3</t>
         </is>
@@ -1354,261 +2798,261 @@
       <c r="I4" s="3" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>年間退職者数</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C6" s="42" t="n"/>
+      <c r="E6" s="41" t="inlineStr">
         <is>
           <t>年間離職率</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="F6" s="42" t="n"/>
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>月平均退職者数</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n"/>
+      <c r="I6" s="42" t="n"/>
     </row>
     <row r="7" ht="38" customHeight="1">
-      <c r="B7" s="6">
+      <c r="B7" s="43">
         <f>'月次推移'!N16+'月次推移'!N17</f>
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="E7" s="8">
+      <c r="C7" s="44" t="n"/>
+      <c r="E7" s="45">
         <f>('月次推移'!N16+'月次推移'!N17)/AVERAGE('月次推移'!B8:M8)</f>
         <v>0.7676767677</v>
       </c>
-      <c r="F7" s="7" t="n"/>
-      <c r="H7" s="9">
+      <c r="F7" s="44" t="n"/>
+      <c r="H7" s="46">
         <f>('月次推移'!N16+'月次推移'!N17)/12</f>
         <v>1.5833333333</v>
       </c>
-      <c r="I7" s="7" t="n"/>
+      <c r="I7" s="44" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>正社員17名・派遣2名</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="C8" s="48" t="n"/>
+      <c r="E8" s="47" t="inlineStr">
         <is>
           <t>年間退職者数 ÷ 平均月初稼働数</t>
         </is>
       </c>
-      <c r="F8" s="11" t="n"/>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="F8" s="48" t="n"/>
+      <c r="H8" s="47" t="inlineStr">
         <is>
           <t>12ヶ月中11ヶ月で退職が発生</t>
         </is>
       </c>
-      <c r="I8" s="11" t="n"/>
+      <c r="I8" s="48" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>年間採用者数</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="C10" s="42" t="n"/>
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>年間の純増減</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="F10" s="42" t="n"/>
+      <c r="H10" s="41" t="inlineStr">
         <is>
           <t>期末の過不足</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n"/>
+      <c r="I10" s="42" t="n"/>
     </row>
     <row r="11" ht="38" customHeight="1">
-      <c r="B11" s="13">
+      <c r="B11" s="50">
         <f>'月次推移'!N11+'月次推移'!N12</f>
         <v>23</v>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="E11" s="14">
+      <c r="C11" s="44" t="n"/>
+      <c r="E11" s="51">
         <f>'月次推移'!N14-'月次推移'!N20</f>
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="n"/>
-      <c r="H11" s="15">
+      <c r="F11" s="44" t="n"/>
+      <c r="H11" s="52">
         <f>'月次推移'!M23</f>
         <v>-5</v>
       </c>
-      <c r="I11" s="7" t="n"/>
+      <c r="I11" s="44" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>正社員21名・派遣2名</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="C12" s="48" t="n"/>
+      <c r="E12" s="47" t="inlineStr">
         <is>
           <t>採用23名 − 離脱23名</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="F12" s="48" t="n"/>
+      <c r="H12" s="47" t="inlineStr">
         <is>
           <t>2026年8月末　必要数25名に対して</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n"/>
+      <c r="I12" s="48" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="53" t="inlineStr">
         <is>
           <t>現状の課題</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>1.　退職が恒常的に発生し、年間離職率は76.8%に達する</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">　　12ヶ月で19名（正社員17名・派遣2名）が退職。月平均1.6名のペースで欠員が発生し続けている。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
         <is>
           <t>2.　年間23名を採用しても、同数の23名が離脱し純増はゼロ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">　　入（採用・異動）23名に対し、出（退職19名＋長期欠勤等による離脱4名）23名。採用は欠員補充に費やされ、体制の積み増しに至っていない。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="54" t="inlineStr">
         <is>
           <t>3.　必要数の増加（20名→25名）に体制が追いつかず、期末時点で▲5名の欠員</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">　　必要数が20名から25名へ引き上げられた一方、稼働数は期首・期末とも20名で横ばい。2026年7月以降は必要数を下回り、8月末は稼働率80%（20名／25名）の状態にある。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>4.　現行の採用手法では、退職ペースを上回る採用が実現できていない</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">　　欠員解消（5名）に加え、今後も想定される年間19名規模の退職補充が必要。採用母集団の拡大が不可欠である。</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="53" t="inlineStr">
         <is>
           <t>参考試算：今後1年間に必要となる採用数</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B25" s="56" t="inlineStr">
         <is>
           <t>① 現時点の欠員（2026年8月末）</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="21">
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="58">
         <f>-'月次推移'!M23</f>
         <v>5</v>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="59" t="inlineStr">
         <is>
           <t>必要数25名 − 稼働数20名</t>
         </is>
       </c>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="23" t="n"/>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="57" t="n"/>
+      <c r="I25" s="60" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="56" t="inlineStr">
         <is>
           <t>② 今後1年間の想定退職者数</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="21">
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="58">
         <f>'月次推移'!N16+'月次推移'!N17</f>
         <v>19</v>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="59" t="inlineStr">
         <is>
           <t>直近12ヶ月の実績と同水準で推移すると仮定</t>
         </is>
       </c>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
-      <c r="I26" s="23" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n"/>
+      <c r="I26" s="60" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>③ 必要採用数（① ＋ ②）</t>
         </is>
       </c>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="26">
+      <c r="C27" s="62" t="n"/>
+      <c r="D27" s="62" t="n"/>
+      <c r="E27" s="63">
         <f>E25+E26</f>
         <v>24</v>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="64" t="inlineStr">
         <is>
           <t>欠員解消および退職補充に要する年間採用数</t>
         </is>
       </c>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="28" t="n"/>
+      <c r="G27" s="62" t="n"/>
+      <c r="H27" s="62" t="n"/>
+      <c r="I27" s="65" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>※ 上記②は直近12ヶ月の退職実績（19名）を前提とした試算値であり、実績値ではない。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>出典：HND MMチーム 人員推移管理表（2025年9月〜2026年8月実績）　／　明細は「月次推移」シート参照</t>
         </is>
@@ -1661,7 +3105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002F5597"/>
@@ -1688,14 +3132,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>HND MMチーム　人員推移（2025年9月〜2026年8月）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>採用媒体の活用に関する稟議　添付資料　2/3　（月次明細）　／　単位：名</t>
         </is>
@@ -1718,959 +3162,959 @@
       <c r="N3" s="3" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>項　目</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
         <is>
           <t>2025年</t>
         </is>
       </c>
-      <c r="C4" s="31" t="n"/>
-      <c r="D4" s="31" t="n"/>
-      <c r="E4" s="31" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="31" t="inlineStr">
+      <c r="C4" s="68" t="n"/>
+      <c r="D4" s="68" t="n"/>
+      <c r="E4" s="68" t="n"/>
+      <c r="F4" s="68" t="n"/>
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>2026年</t>
         </is>
       </c>
-      <c r="H4" s="31" t="n"/>
-      <c r="I4" s="31" t="n"/>
-      <c r="J4" s="31" t="n"/>
-      <c r="K4" s="31" t="n"/>
-      <c r="L4" s="31" t="n"/>
-      <c r="M4" s="31" t="n"/>
-      <c r="N4" s="31" t="inlineStr">
+      <c r="H4" s="68" t="n"/>
+      <c r="I4" s="68" t="n"/>
+      <c r="J4" s="68" t="n"/>
+      <c r="K4" s="68" t="n"/>
+      <c r="L4" s="68" t="n"/>
+      <c r="M4" s="68" t="n"/>
+      <c r="N4" s="68" t="inlineStr">
         <is>
           <t>年間計</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="32" t="n"/>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="A5" s="69" t="n"/>
+      <c r="B5" s="69" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="69" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="69" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="69" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" s="69" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="69" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="69" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="J5" s="32" t="inlineStr">
+      <c r="J5" s="69" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="K5" s="69" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="L5" s="32" t="inlineStr">
+      <c r="L5" s="69" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="M5" s="32" t="inlineStr">
+      <c r="M5" s="69" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="N5" s="32" t="n"/>
+      <c r="N5" s="69" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>体　制</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n"/>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="35" t="n"/>
+      <c r="B6" s="71" t="n"/>
+      <c r="C6" s="71" t="n"/>
+      <c r="D6" s="71" t="n"/>
+      <c r="E6" s="71" t="n"/>
+      <c r="F6" s="71" t="n"/>
+      <c r="G6" s="71" t="n"/>
+      <c r="H6" s="71" t="n"/>
+      <c r="I6" s="71" t="n"/>
+      <c r="J6" s="71" t="n"/>
+      <c r="K6" s="71" t="n"/>
+      <c r="L6" s="71" t="n"/>
+      <c r="M6" s="71" t="n"/>
+      <c r="N6" s="72" t="n"/>
     </row>
     <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>必要数 (a)</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="73" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="D7" s="36" t="n">
+      <c r="D7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="36" t="n">
+      <c r="E7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="36" t="n">
+      <c r="G7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="H7" s="36" t="n">
+      <c r="H7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="I7" s="36" t="n">
+      <c r="I7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="J7" s="36" t="n">
+      <c r="J7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="K7" s="36" t="n">
+      <c r="K7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="L7" s="36" t="n">
+      <c r="L7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="M7" s="36" t="n">
+      <c r="M7" s="73" t="n">
         <v>25</v>
       </c>
-      <c r="N7" s="37" t="inlineStr">
+      <c r="N7" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="75" t="inlineStr">
         <is>
           <t>月初稼働数 (b)</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="76" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="77">
         <f>B22</f>
         <v>19</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="77">
         <f>C22</f>
         <v>22</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="77">
         <f>D22</f>
         <v>27</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="77">
         <f>E22</f>
         <v>29</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="77">
         <f>F22</f>
         <v>27</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="77">
         <f>G22</f>
         <v>27</v>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="77">
         <f>H22</f>
         <v>26</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J8" s="77">
         <f>I22</f>
         <v>26</v>
       </c>
-      <c r="K8" s="40">
+      <c r="K8" s="77">
         <f>J22</f>
         <v>26</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L8" s="77">
         <f>K22</f>
         <v>25</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M8" s="77">
         <f>L22</f>
         <v>23</v>
       </c>
-      <c r="N8" s="41" t="inlineStr">
+      <c r="N8" s="78" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>差異 (b − a)</t>
         </is>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="79">
         <f>B8-B7</f>
         <v>0</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="79">
         <f>C8-C7</f>
         <v>-6</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="79">
         <f>D8-D7</f>
         <v>-3</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="79">
         <f>E8-E7</f>
         <v>2</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="79">
         <f>F8-F7</f>
         <v>4</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="79">
         <f>G8-G7</f>
         <v>2</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="79">
         <f>H8-H7</f>
         <v>2</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="79">
         <f>I8-I7</f>
         <v>1</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="79">
         <f>J8-J7</f>
         <v>1</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="79">
         <f>K8-K7</f>
         <v>1</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="79">
         <f>L8-L7</f>
         <v>0</v>
       </c>
-      <c r="M9" s="42">
+      <c r="M9" s="79">
         <f>M8-M7</f>
         <v>-2</v>
       </c>
-      <c r="N9" s="37" t="inlineStr">
+      <c r="N9" s="74" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t>入（増員）</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="34" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
-      <c r="G10" s="34" t="n"/>
-      <c r="H10" s="34" t="n"/>
-      <c r="I10" s="34" t="n"/>
-      <c r="J10" s="34" t="n"/>
-      <c r="K10" s="34" t="n"/>
-      <c r="L10" s="34" t="n"/>
-      <c r="M10" s="34" t="n"/>
-      <c r="N10" s="35" t="n"/>
+      <c r="B10" s="71" t="n"/>
+      <c r="C10" s="71" t="n"/>
+      <c r="D10" s="71" t="n"/>
+      <c r="E10" s="71" t="n"/>
+      <c r="F10" s="71" t="n"/>
+      <c r="G10" s="71" t="n"/>
+      <c r="H10" s="71" t="n"/>
+      <c r="I10" s="71" t="n"/>
+      <c r="J10" s="71" t="n"/>
+      <c r="K10" s="71" t="n"/>
+      <c r="L10" s="71" t="n"/>
+      <c r="M10" s="71" t="n"/>
+      <c r="N10" s="72" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>採用数（正社員）</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="36" t="n">
+      <c r="B11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="36" t="n">
+      <c r="E11" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="36" t="n">
+      <c r="F11" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="36" t="n">
+      <c r="H11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="43">
+      <c r="J11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="80">
         <f>SUM(B11:M11)</f>
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>採用数（派遣）</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="43">
+      <c r="B12" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="80">
         <f>SUM(B12:M12)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>異動（入）</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="43">
+      <c r="B13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="80">
         <f>SUM(B13:M13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>入 合計</t>
         </is>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="82">
         <f>SUM(B11:B13)</f>
         <v>1</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="82">
         <f>SUM(C11:C13)</f>
         <v>4</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="82">
         <f>SUM(D11:D13)</f>
         <v>7</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="82">
         <f>SUM(E11:E13)</f>
         <v>4</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="82">
         <f>SUM(F11:F13)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="82">
         <f>SUM(G11:G13)</f>
         <v>3</v>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="82">
         <f>SUM(H11:H13)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="82">
         <f>SUM(I11:I13)</f>
         <v>3</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="82">
         <f>SUM(J11:J13)</f>
         <v>0</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="82">
         <f>SUM(K11:K13)</f>
         <v>0</v>
       </c>
-      <c r="L14" s="45">
+      <c r="L14" s="82">
         <f>SUM(L11:L13)</f>
         <v>0</v>
       </c>
-      <c r="M14" s="45">
+      <c r="M14" s="82">
         <f>SUM(M11:M13)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="43">
+      <c r="N14" s="80">
         <f>SUM(B14:M14)</f>
         <v>23</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>出（減員）</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="34" t="n"/>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="34" t="n"/>
-      <c r="J15" s="34" t="n"/>
-      <c r="K15" s="34" t="n"/>
-      <c r="L15" s="34" t="n"/>
-      <c r="M15" s="34" t="n"/>
-      <c r="N15" s="35" t="n"/>
+      <c r="B15" s="71" t="n"/>
+      <c r="C15" s="71" t="n"/>
+      <c r="D15" s="71" t="n"/>
+      <c r="E15" s="71" t="n"/>
+      <c r="F15" s="71" t="n"/>
+      <c r="G15" s="71" t="n"/>
+      <c r="H15" s="71" t="n"/>
+      <c r="I15" s="71" t="n"/>
+      <c r="J15" s="71" t="n"/>
+      <c r="K15" s="71" t="n"/>
+      <c r="L15" s="71" t="n"/>
+      <c r="M15" s="71" t="n"/>
+      <c r="N15" s="72" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>退職数（正社員）</t>
         </is>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="36" t="n">
+      <c r="C16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="36" t="n">
+      <c r="G16" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="36" t="n">
+      <c r="H16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" s="43">
+      <c r="M16" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="80">
         <f>SUM(B16:M16)</f>
         <v>17</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>退職数（派遣）</t>
         </is>
       </c>
-      <c r="B17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="43">
+      <c r="B17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="80">
         <f>SUM(B17:M17)</f>
         <v>2</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>長期欠勤等による離脱者数</t>
         </is>
       </c>
-      <c r="B18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="36" t="n">
+      <c r="B18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="36" t="n">
+      <c r="J18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="N18" s="43">
+      <c r="N18" s="80">
         <f>SUM(B18:M18)</f>
         <v>4</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>異動（出）</t>
         </is>
       </c>
-      <c r="B19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="43">
+      <c r="B19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="80">
         <f>SUM(B19:M19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="81" t="inlineStr">
         <is>
           <t>出 合計</t>
         </is>
       </c>
-      <c r="B20" s="45">
+      <c r="B20" s="82">
         <f>SUM(B16:B19)</f>
         <v>2</v>
       </c>
-      <c r="C20" s="45">
+      <c r="C20" s="82">
         <f>SUM(C16:C19)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="82">
         <f>SUM(D16:D19)</f>
         <v>2</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="82">
         <f>SUM(E16:E19)</f>
         <v>2</v>
       </c>
-      <c r="F20" s="45">
+      <c r="F20" s="82">
         <f>SUM(F16:F19)</f>
         <v>3</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G20" s="82">
         <f>SUM(G16:G19)</f>
         <v>3</v>
       </c>
-      <c r="H20" s="45">
+      <c r="H20" s="82">
         <f>SUM(H16:H19)</f>
         <v>1</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="82">
         <f>SUM(I16:I19)</f>
         <v>3</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="82">
         <f>SUM(J16:J19)</f>
         <v>0</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="82">
         <f>SUM(K16:K19)</f>
         <v>1</v>
       </c>
-      <c r="L20" s="45">
+      <c r="L20" s="82">
         <f>SUM(L16:L19)</f>
         <v>2</v>
       </c>
-      <c r="M20" s="45">
+      <c r="M20" s="82">
         <f>SUM(M16:M19)</f>
         <v>3</v>
       </c>
-      <c r="N20" s="43">
+      <c r="N20" s="80">
         <f>SUM(B20:M20)</f>
         <v>23</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="70" t="inlineStr">
         <is>
           <t>結　果</t>
         </is>
       </c>
-      <c r="B21" s="34" t="n"/>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="34" t="n"/>
-      <c r="J21" s="34" t="n"/>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n"/>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="35" t="n"/>
+      <c r="B21" s="71" t="n"/>
+      <c r="C21" s="71" t="n"/>
+      <c r="D21" s="71" t="n"/>
+      <c r="E21" s="71" t="n"/>
+      <c r="F21" s="71" t="n"/>
+      <c r="G21" s="71" t="n"/>
+      <c r="H21" s="71" t="n"/>
+      <c r="I21" s="71" t="n"/>
+      <c r="J21" s="71" t="n"/>
+      <c r="K21" s="71" t="n"/>
+      <c r="L21" s="71" t="n"/>
+      <c r="M21" s="71" t="n"/>
+      <c r="N21" s="72" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="A22" s="75" t="inlineStr">
         <is>
           <t>月末稼働数 (c)</t>
         </is>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="77">
         <f>B8+B14-B20</f>
         <v>19</v>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="77">
         <f>C8+C14-C20</f>
         <v>22</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="77">
         <f>D8+D14-D20</f>
         <v>27</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="77">
         <f>E8+E14-E20</f>
         <v>29</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="77">
         <f>F8+F14-F20</f>
         <v>27</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="77">
         <f>G8+G14-G20</f>
         <v>27</v>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="77">
         <f>H8+H14-H20</f>
         <v>26</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="77">
         <f>I8+I14-I20</f>
         <v>26</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="77">
         <f>J8+J14-J20</f>
         <v>26</v>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="77">
         <f>K8+K14-K20</f>
         <v>25</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="77">
         <f>L8+L14-L20</f>
         <v>23</v>
       </c>
-      <c r="M22" s="40">
+      <c r="M22" s="77">
         <f>M8+M14-M20</f>
         <v>20</v>
       </c>
-      <c r="N22" s="41" t="inlineStr">
+      <c r="N22" s="78" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="46" t="inlineStr">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>過不足 (c − a)</t>
         </is>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="84">
         <f>B22-B7</f>
         <v>-1</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="84">
         <f>C22-C7</f>
         <v>-3</v>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="84">
         <f>D22-D7</f>
         <v>2</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="84">
         <f>E22-E7</f>
         <v>4</v>
       </c>
-      <c r="F23" s="47">
+      <c r="F23" s="84">
         <f>F22-F7</f>
         <v>2</v>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="84">
         <f>G22-G7</f>
         <v>2</v>
       </c>
-      <c r="H23" s="47">
+      <c r="H23" s="84">
         <f>H22-H7</f>
         <v>1</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="84">
         <f>I22-I7</f>
         <v>1</v>
       </c>
-      <c r="J23" s="47">
+      <c r="J23" s="84">
         <f>J22-J7</f>
         <v>1</v>
       </c>
-      <c r="K23" s="47">
+      <c r="K23" s="84">
         <f>K22-K7</f>
         <v>0</v>
       </c>
-      <c r="L23" s="47">
+      <c r="L23" s="84">
         <f>L22-L7</f>
         <v>-2</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="84">
         <f>M22-M7</f>
         <v>-5</v>
       </c>
-      <c r="N23" s="48" t="inlineStr">
+      <c r="N23" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>【注記】</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="50" t="inlineStr">
+      <c r="A26" s="87" t="inlineStr">
         <is>
           <t>1. 数値の単位は「名」。青字セルは実績入力値、黒字セルは計算式による自動算出。マイナスは「▲」（赤字）で表示。</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="50" t="inlineStr">
+      <c r="A27" s="87" t="inlineStr">
         <is>
           <t>2. 「月初稼働数(b)」は前月の「月末稼働数(c)」を引き継ぐ（2025年9月のみ実績入力）。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="50" t="inlineStr">
+      <c r="A28" s="87" t="inlineStr">
         <is>
           <t>3. 「月末稼働数(c)」＝ 月初稼働数(b) ＋ 入 合計 − 出 合計。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="50" t="inlineStr">
+      <c r="A29" s="87" t="inlineStr">
         <is>
           <t>4. 「長期欠勤等による離脱者数」は在籍のままラインに入れない人数を指し、退職数には含まない。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="50" t="inlineStr">
+      <c r="A30" s="87" t="inlineStr">
         <is>
           <t>5. 「年間計」欄の「—」は、月次の累計になじまない項目（在籍数・過不足）であることを示す。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="50" t="inlineStr">
+      <c r="A31" s="87" t="inlineStr">
         <is>
           <t>6. 出典：HND MMチーム 人員推移管理表（2025年9月〜2026年8月実績）。</t>
         </is>
@@ -2697,12 +4141,12 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:M9">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23:M23">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2712,7 +4156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="002F5597"/>
@@ -2739,14 +4183,14 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>HND MMチーム　人員推移グラフ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>対象期間：2025年9月〜2026年8月　／　採用媒体の活用に関する稟議　添付資料　3/3</t>
         </is>
@@ -2768,815 +4212,815 @@
       <c r="N4" s="3" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="51" t="inlineStr">
+      <c r="B24" s="88" t="inlineStr">
         <is>
           <t>月別数値：必要数・稼働数</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="52" t="inlineStr">
+      <c r="B25" s="89" t="inlineStr">
         <is>
           <t>項　目</t>
         </is>
       </c>
-      <c r="C25" s="52" t="inlineStr">
+      <c r="C25" s="89" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="89" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="E25" s="52" t="inlineStr">
+      <c r="E25" s="89" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="F25" s="52" t="inlineStr">
+      <c r="F25" s="89" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="G25" s="52" t="inlineStr">
+      <c r="G25" s="89" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="H25" s="52" t="inlineStr">
+      <c r="H25" s="89" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="I25" s="52" t="inlineStr">
+      <c r="I25" s="89" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="J25" s="52" t="inlineStr">
+      <c r="J25" s="89" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="K25" s="52" t="inlineStr">
+      <c r="K25" s="89" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="L25" s="52" t="inlineStr">
+      <c r="L25" s="89" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="M25" s="52" t="inlineStr">
+      <c r="M25" s="89" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N25" s="52" t="inlineStr">
+      <c r="N25" s="89" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="53" t="inlineStr">
+      <c r="B26" s="90" t="inlineStr">
         <is>
           <t>必要数 (a)</t>
         </is>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="91">
         <f>'月次推移'!B7</f>
         <v>20</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="91">
         <f>'月次推移'!C7</f>
         <v>25</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="91">
         <f>'月次推移'!D7</f>
         <v>25</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="91">
         <f>'月次推移'!E7</f>
         <v>25</v>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="91">
         <f>'月次推移'!F7</f>
         <v>25</v>
       </c>
-      <c r="H26" s="54">
+      <c r="H26" s="91">
         <f>'月次推移'!G7</f>
         <v>25</v>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="91">
         <f>'月次推移'!H7</f>
         <v>25</v>
       </c>
-      <c r="J26" s="54">
+      <c r="J26" s="91">
         <f>'月次推移'!I7</f>
         <v>25</v>
       </c>
-      <c r="K26" s="54">
+      <c r="K26" s="91">
         <f>'月次推移'!J7</f>
         <v>25</v>
       </c>
-      <c r="L26" s="54">
+      <c r="L26" s="91">
         <f>'月次推移'!K7</f>
         <v>25</v>
       </c>
-      <c r="M26" s="54">
+      <c r="M26" s="91">
         <f>'月次推移'!L7</f>
         <v>25</v>
       </c>
-      <c r="N26" s="55">
+      <c r="N26" s="92">
         <f>'月次推移'!M7</f>
         <v>25</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="53" t="inlineStr">
+      <c r="B27" s="90" t="inlineStr">
         <is>
           <t>月初稼働数 (b)</t>
         </is>
       </c>
-      <c r="C27" s="54">
+      <c r="C27" s="91">
         <f>'月次推移'!B8</f>
         <v>20</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="91">
         <f>'月次推移'!C8</f>
         <v>19</v>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="91">
         <f>'月次推移'!D8</f>
         <v>22</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="91">
         <f>'月次推移'!E8</f>
         <v>27</v>
       </c>
-      <c r="G27" s="54">
+      <c r="G27" s="91">
         <f>'月次推移'!F8</f>
         <v>29</v>
       </c>
-      <c r="H27" s="54">
+      <c r="H27" s="91">
         <f>'月次推移'!G8</f>
         <v>27</v>
       </c>
-      <c r="I27" s="54">
+      <c r="I27" s="91">
         <f>'月次推移'!H8</f>
         <v>27</v>
       </c>
-      <c r="J27" s="54">
+      <c r="J27" s="91">
         <f>'月次推移'!I8</f>
         <v>26</v>
       </c>
-      <c r="K27" s="54">
+      <c r="K27" s="91">
         <f>'月次推移'!J8</f>
         <v>26</v>
       </c>
-      <c r="L27" s="54">
+      <c r="L27" s="91">
         <f>'月次推移'!K8</f>
         <v>26</v>
       </c>
-      <c r="M27" s="54">
+      <c r="M27" s="91">
         <f>'月次推移'!L8</f>
         <v>25</v>
       </c>
-      <c r="N27" s="55">
+      <c r="N27" s="92">
         <f>'月次推移'!M8</f>
         <v>23</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="56" t="inlineStr">
+      <c r="B28" s="93" t="inlineStr">
         <is>
           <t>月末稼働数 (c)</t>
         </is>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="94">
         <f>'月次推移'!B22</f>
         <v>19</v>
       </c>
-      <c r="D28" s="57">
+      <c r="D28" s="94">
         <f>'月次推移'!C22</f>
         <v>22</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="94">
         <f>'月次推移'!D22</f>
         <v>27</v>
       </c>
-      <c r="F28" s="57">
+      <c r="F28" s="94">
         <f>'月次推移'!E22</f>
         <v>29</v>
       </c>
-      <c r="G28" s="57">
+      <c r="G28" s="94">
         <f>'月次推移'!F22</f>
         <v>27</v>
       </c>
-      <c r="H28" s="57">
+      <c r="H28" s="94">
         <f>'月次推移'!G22</f>
         <v>27</v>
       </c>
-      <c r="I28" s="57">
+      <c r="I28" s="94">
         <f>'月次推移'!H22</f>
         <v>26</v>
       </c>
-      <c r="J28" s="57">
+      <c r="J28" s="94">
         <f>'月次推移'!I22</f>
         <v>26</v>
       </c>
-      <c r="K28" s="57">
+      <c r="K28" s="94">
         <f>'月次推移'!J22</f>
         <v>26</v>
       </c>
-      <c r="L28" s="57">
+      <c r="L28" s="94">
         <f>'月次推移'!K22</f>
         <v>25</v>
       </c>
-      <c r="M28" s="57">
+      <c r="M28" s="94">
         <f>'月次推移'!L22</f>
         <v>23</v>
       </c>
-      <c r="N28" s="58">
+      <c r="N28" s="95">
         <f>'月次推移'!M22</f>
         <v>20</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="96" t="inlineStr">
         <is>
           <t>過不足 (c − a)</t>
         </is>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="97">
         <f>'月次推移'!B23</f>
         <v>-1</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="97">
         <f>'月次推移'!C23</f>
         <v>-3</v>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="97">
         <f>'月次推移'!D23</f>
         <v>2</v>
       </c>
-      <c r="F29" s="60">
+      <c r="F29" s="97">
         <f>'月次推移'!E23</f>
         <v>4</v>
       </c>
-      <c r="G29" s="60">
+      <c r="G29" s="97">
         <f>'月次推移'!F23</f>
         <v>2</v>
       </c>
-      <c r="H29" s="60">
+      <c r="H29" s="97">
         <f>'月次推移'!G23</f>
         <v>2</v>
       </c>
-      <c r="I29" s="60">
+      <c r="I29" s="97">
         <f>'月次推移'!H23</f>
         <v>1</v>
       </c>
-      <c r="J29" s="60">
+      <c r="J29" s="97">
         <f>'月次推移'!I23</f>
         <v>1</v>
       </c>
-      <c r="K29" s="60">
+      <c r="K29" s="97">
         <f>'月次推移'!J23</f>
         <v>1</v>
       </c>
-      <c r="L29" s="60">
+      <c r="L29" s="97">
         <f>'月次推移'!K23</f>
         <v>0</v>
       </c>
-      <c r="M29" s="60">
+      <c r="M29" s="97">
         <f>'月次推移'!L23</f>
         <v>-2</v>
       </c>
-      <c r="N29" s="61">
+      <c r="N29" s="98">
         <f>'月次推移'!M23</f>
         <v>-5</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="B50" s="51" t="inlineStr">
+      <c r="B50" s="88" t="inlineStr">
         <is>
           <t>月別数値：入（増員）・出（減員）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
-      <c r="B51" s="52" t="inlineStr">
+      <c r="B51" s="89" t="inlineStr">
         <is>
           <t>項　目</t>
         </is>
       </c>
-      <c r="C51" s="52" t="inlineStr">
+      <c r="C51" s="89" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="D51" s="52" t="inlineStr">
+      <c r="D51" s="89" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="E51" s="52" t="inlineStr">
+      <c r="E51" s="89" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="F51" s="52" t="inlineStr">
+      <c r="F51" s="89" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="G51" s="52" t="inlineStr">
+      <c r="G51" s="89" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="H51" s="52" t="inlineStr">
+      <c r="H51" s="89" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="I51" s="52" t="inlineStr">
+      <c r="I51" s="89" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="J51" s="52" t="inlineStr">
+      <c r="J51" s="89" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="K51" s="52" t="inlineStr">
+      <c r="K51" s="89" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="L51" s="52" t="inlineStr">
+      <c r="L51" s="89" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="M51" s="52" t="inlineStr">
+      <c r="M51" s="89" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="N51" s="52" t="inlineStr">
+      <c r="N51" s="89" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="53" t="inlineStr">
+      <c r="B52" s="90" t="inlineStr">
         <is>
           <t>採用数（正社員）</t>
         </is>
       </c>
-      <c r="C52" s="54">
+      <c r="C52" s="91">
         <f>'月次推移'!B11</f>
         <v>0</v>
       </c>
-      <c r="D52" s="54">
+      <c r="D52" s="91">
         <f>'月次推移'!C11</f>
         <v>4</v>
       </c>
-      <c r="E52" s="54">
+      <c r="E52" s="91">
         <f>'月次推移'!D11</f>
         <v>6</v>
       </c>
-      <c r="F52" s="54">
+      <c r="F52" s="91">
         <f>'月次推移'!E11</f>
         <v>4</v>
       </c>
-      <c r="G52" s="54">
+      <c r="G52" s="91">
         <f>'月次推移'!F11</f>
         <v>1</v>
       </c>
-      <c r="H52" s="54">
+      <c r="H52" s="91">
         <f>'月次推移'!G11</f>
         <v>3</v>
       </c>
-      <c r="I52" s="54">
+      <c r="I52" s="91">
         <f>'月次推移'!H11</f>
         <v>0</v>
       </c>
-      <c r="J52" s="54">
+      <c r="J52" s="91">
         <f>'月次推移'!I11</f>
         <v>3</v>
       </c>
-      <c r="K52" s="54">
+      <c r="K52" s="91">
         <f>'月次推移'!J11</f>
         <v>0</v>
       </c>
-      <c r="L52" s="54">
+      <c r="L52" s="91">
         <f>'月次推移'!K11</f>
         <v>0</v>
       </c>
-      <c r="M52" s="54">
+      <c r="M52" s="91">
         <f>'月次推移'!L11</f>
         <v>0</v>
       </c>
-      <c r="N52" s="55">
+      <c r="N52" s="92">
         <f>'月次推移'!M11</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="B53" s="53" t="inlineStr">
+      <c r="B53" s="90" t="inlineStr">
         <is>
           <t>採用数（派遣）</t>
         </is>
       </c>
-      <c r="C53" s="54">
+      <c r="C53" s="91">
         <f>'月次推移'!B12</f>
         <v>1</v>
       </c>
-      <c r="D53" s="54">
+      <c r="D53" s="91">
         <f>'月次推移'!C12</f>
         <v>0</v>
       </c>
-      <c r="E53" s="54">
+      <c r="E53" s="91">
         <f>'月次推移'!D12</f>
         <v>1</v>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="91">
         <f>'月次推移'!E12</f>
         <v>0</v>
       </c>
-      <c r="G53" s="54">
+      <c r="G53" s="91">
         <f>'月次推移'!F12</f>
         <v>0</v>
       </c>
-      <c r="H53" s="54">
+      <c r="H53" s="91">
         <f>'月次推移'!G12</f>
         <v>0</v>
       </c>
-      <c r="I53" s="54">
+      <c r="I53" s="91">
         <f>'月次推移'!H12</f>
         <v>0</v>
       </c>
-      <c r="J53" s="54">
+      <c r="J53" s="91">
         <f>'月次推移'!I12</f>
         <v>0</v>
       </c>
-      <c r="K53" s="54">
+      <c r="K53" s="91">
         <f>'月次推移'!J12</f>
         <v>0</v>
       </c>
-      <c r="L53" s="54">
+      <c r="L53" s="91">
         <f>'月次推移'!K12</f>
         <v>0</v>
       </c>
-      <c r="M53" s="54">
+      <c r="M53" s="91">
         <f>'月次推移'!L12</f>
         <v>0</v>
       </c>
-      <c r="N53" s="55">
+      <c r="N53" s="92">
         <f>'月次推移'!M12</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="56" t="inlineStr">
+      <c r="B54" s="93" t="inlineStr">
         <is>
           <t>入 合計</t>
         </is>
       </c>
-      <c r="C54" s="57">
+      <c r="C54" s="94">
         <f>'月次推移'!B14</f>
         <v>1</v>
       </c>
-      <c r="D54" s="57">
+      <c r="D54" s="94">
         <f>'月次推移'!C14</f>
         <v>4</v>
       </c>
-      <c r="E54" s="57">
+      <c r="E54" s="94">
         <f>'月次推移'!D14</f>
         <v>7</v>
       </c>
-      <c r="F54" s="57">
+      <c r="F54" s="94">
         <f>'月次推移'!E14</f>
         <v>4</v>
       </c>
-      <c r="G54" s="57">
+      <c r="G54" s="94">
         <f>'月次推移'!F14</f>
         <v>1</v>
       </c>
-      <c r="H54" s="57">
+      <c r="H54" s="94">
         <f>'月次推移'!G14</f>
         <v>3</v>
       </c>
-      <c r="I54" s="57">
+      <c r="I54" s="94">
         <f>'月次推移'!H14</f>
         <v>0</v>
       </c>
-      <c r="J54" s="57">
+      <c r="J54" s="94">
         <f>'月次推移'!I14</f>
         <v>3</v>
       </c>
-      <c r="K54" s="57">
+      <c r="K54" s="94">
         <f>'月次推移'!J14</f>
         <v>0</v>
       </c>
-      <c r="L54" s="57">
+      <c r="L54" s="94">
         <f>'月次推移'!K14</f>
         <v>0</v>
       </c>
-      <c r="M54" s="57">
+      <c r="M54" s="94">
         <f>'月次推移'!L14</f>
         <v>0</v>
       </c>
-      <c r="N54" s="58">
+      <c r="N54" s="95">
         <f>'月次推移'!M14</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="53" t="inlineStr">
+      <c r="B55" s="90" t="inlineStr">
         <is>
           <t>退職数（正社員）</t>
         </is>
       </c>
-      <c r="C55" s="54">
+      <c r="C55" s="91">
         <f>'月次推移'!B16</f>
         <v>2</v>
       </c>
-      <c r="D55" s="54">
+      <c r="D55" s="91">
         <f>'月次推移'!C16</f>
         <v>1</v>
       </c>
-      <c r="E55" s="54">
+      <c r="E55" s="91">
         <f>'月次推移'!D16</f>
         <v>1</v>
       </c>
-      <c r="F55" s="54">
+      <c r="F55" s="91">
         <f>'月次推移'!E16</f>
         <v>1</v>
       </c>
-      <c r="G55" s="54">
+      <c r="G55" s="91">
         <f>'月次推移'!F16</f>
         <v>3</v>
       </c>
-      <c r="H55" s="54">
+      <c r="H55" s="91">
         <f>'月次推移'!G16</f>
         <v>3</v>
       </c>
-      <c r="I55" s="54">
+      <c r="I55" s="91">
         <f>'月次推移'!H16</f>
         <v>1</v>
       </c>
-      <c r="J55" s="54">
+      <c r="J55" s="91">
         <f>'月次推移'!I16</f>
         <v>1</v>
       </c>
-      <c r="K55" s="54">
+      <c r="K55" s="91">
         <f>'月次推移'!J16</f>
         <v>0</v>
       </c>
-      <c r="L55" s="54">
+      <c r="L55" s="91">
         <f>'月次推移'!K16</f>
         <v>1</v>
       </c>
-      <c r="M55" s="54">
+      <c r="M55" s="91">
         <f>'月次推移'!L16</f>
         <v>2</v>
       </c>
-      <c r="N55" s="55">
+      <c r="N55" s="92">
         <f>'月次推移'!M16</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="B56" s="53" t="inlineStr">
+      <c r="B56" s="90" t="inlineStr">
         <is>
           <t>退職数（派遣）</t>
         </is>
       </c>
-      <c r="C56" s="54">
+      <c r="C56" s="91">
         <f>'月次推移'!B17</f>
         <v>0</v>
       </c>
-      <c r="D56" s="54">
+      <c r="D56" s="91">
         <f>'月次推移'!C17</f>
         <v>0</v>
       </c>
-      <c r="E56" s="54">
+      <c r="E56" s="91">
         <f>'月次推移'!D17</f>
         <v>1</v>
       </c>
-      <c r="F56" s="54">
+      <c r="F56" s="91">
         <f>'月次推移'!E17</f>
         <v>1</v>
       </c>
-      <c r="G56" s="54">
+      <c r="G56" s="91">
         <f>'月次推移'!F17</f>
         <v>0</v>
       </c>
-      <c r="H56" s="54">
+      <c r="H56" s="91">
         <f>'月次推移'!G17</f>
         <v>0</v>
       </c>
-      <c r="I56" s="54">
+      <c r="I56" s="91">
         <f>'月次推移'!H17</f>
         <v>0</v>
       </c>
-      <c r="J56" s="54">
+      <c r="J56" s="91">
         <f>'月次推移'!I17</f>
         <v>0</v>
       </c>
-      <c r="K56" s="54">
+      <c r="K56" s="91">
         <f>'月次推移'!J17</f>
         <v>0</v>
       </c>
-      <c r="L56" s="54">
+      <c r="L56" s="91">
         <f>'月次推移'!K17</f>
         <v>0</v>
       </c>
-      <c r="M56" s="54">
+      <c r="M56" s="91">
         <f>'月次推移'!L17</f>
         <v>0</v>
       </c>
-      <c r="N56" s="55">
+      <c r="N56" s="92">
         <f>'月次推移'!M17</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="53" t="inlineStr">
+      <c r="B57" s="90" t="inlineStr">
         <is>
           <t>長期欠勤等による離脱</t>
         </is>
       </c>
-      <c r="C57" s="54">
+      <c r="C57" s="91">
         <f>'月次推移'!B18</f>
         <v>0</v>
       </c>
-      <c r="D57" s="54">
+      <c r="D57" s="91">
         <f>'月次推移'!C18</f>
         <v>0</v>
       </c>
-      <c r="E57" s="54">
+      <c r="E57" s="91">
         <f>'月次推移'!D18</f>
         <v>0</v>
       </c>
-      <c r="F57" s="54">
+      <c r="F57" s="91">
         <f>'月次推移'!E18</f>
         <v>0</v>
       </c>
-      <c r="G57" s="54">
+      <c r="G57" s="91">
         <f>'月次推移'!F18</f>
         <v>0</v>
       </c>
-      <c r="H57" s="54">
+      <c r="H57" s="91">
         <f>'月次推移'!G18</f>
         <v>0</v>
       </c>
-      <c r="I57" s="54">
+      <c r="I57" s="91">
         <f>'月次推移'!H18</f>
         <v>0</v>
       </c>
-      <c r="J57" s="54">
+      <c r="J57" s="91">
         <f>'月次推移'!I18</f>
         <v>2</v>
       </c>
-      <c r="K57" s="54">
+      <c r="K57" s="91">
         <f>'月次推移'!J18</f>
         <v>0</v>
       </c>
-      <c r="L57" s="54">
+      <c r="L57" s="91">
         <f>'月次推移'!K18</f>
         <v>0</v>
       </c>
-      <c r="M57" s="54">
+      <c r="M57" s="91">
         <f>'月次推移'!L18</f>
         <v>0</v>
       </c>
-      <c r="N57" s="55">
+      <c r="N57" s="92">
         <f>'月次推移'!M18</f>
         <v>2</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="56" t="inlineStr">
+      <c r="B58" s="93" t="inlineStr">
         <is>
           <t>出 合計</t>
         </is>
       </c>
-      <c r="C58" s="57">
+      <c r="C58" s="94">
         <f>'月次推移'!B20</f>
         <v>2</v>
       </c>
-      <c r="D58" s="57">
+      <c r="D58" s="94">
         <f>'月次推移'!C20</f>
         <v>1</v>
       </c>
-      <c r="E58" s="57">
+      <c r="E58" s="94">
         <f>'月次推移'!D20</f>
         <v>2</v>
       </c>
-      <c r="F58" s="57">
+      <c r="F58" s="94">
         <f>'月次推移'!E20</f>
         <v>2</v>
       </c>
-      <c r="G58" s="57">
+      <c r="G58" s="94">
         <f>'月次推移'!F20</f>
         <v>3</v>
       </c>
-      <c r="H58" s="57">
+      <c r="H58" s="94">
         <f>'月次推移'!G20</f>
         <v>3</v>
       </c>
-      <c r="I58" s="57">
+      <c r="I58" s="94">
         <f>'月次推移'!H20</f>
         <v>1</v>
       </c>
-      <c r="J58" s="57">
+      <c r="J58" s="94">
         <f>'月次推移'!I20</f>
         <v>3</v>
       </c>
-      <c r="K58" s="57">
+      <c r="K58" s="94">
         <f>'月次推移'!J20</f>
         <v>0</v>
       </c>
-      <c r="L58" s="57">
+      <c r="L58" s="94">
         <f>'月次推移'!K20</f>
         <v>1</v>
       </c>
-      <c r="M58" s="57">
+      <c r="M58" s="94">
         <f>'月次推移'!L20</f>
         <v>2</v>
       </c>
-      <c r="N58" s="58">
+      <c r="N58" s="95">
         <f>'月次推移'!M20</f>
         <v>3</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="59" t="inlineStr">
+      <c r="B59" s="96" t="inlineStr">
         <is>
           <t>純増減（入 − 出）</t>
         </is>
       </c>
-      <c r="C59" s="60">
+      <c r="C59" s="97">
         <f>'月次推移'!B14-'月次推移'!B20</f>
         <v>-1</v>
       </c>
-      <c r="D59" s="60">
+      <c r="D59" s="97">
         <f>'月次推移'!C14-'月次推移'!C20</f>
         <v>3</v>
       </c>
-      <c r="E59" s="60">
+      <c r="E59" s="97">
         <f>'月次推移'!D14-'月次推移'!D20</f>
         <v>5</v>
       </c>
-      <c r="F59" s="60">
+      <c r="F59" s="97">
         <f>'月次推移'!E14-'月次推移'!E20</f>
         <v>2</v>
       </c>
-      <c r="G59" s="60">
+      <c r="G59" s="97">
         <f>'月次推移'!F14-'月次推移'!F20</f>
         <v>-2</v>
       </c>
-      <c r="H59" s="60">
+      <c r="H59" s="97">
         <f>'月次推移'!G14-'月次推移'!G20</f>
         <v>0</v>
       </c>
-      <c r="I59" s="60">
+      <c r="I59" s="97">
         <f>'月次推移'!H14-'月次推移'!H20</f>
         <v>-1</v>
       </c>
-      <c r="J59" s="60">
+      <c r="J59" s="97">
         <f>'月次推移'!I14-'月次推移'!I20</f>
         <v>0</v>
       </c>
-      <c r="K59" s="60">
+      <c r="K59" s="97">
         <f>'月次推移'!J14-'月次推移'!J20</f>
         <v>0</v>
       </c>
-      <c r="L59" s="60">
+      <c r="L59" s="97">
         <f>'月次推移'!K14-'月次推移'!K20</f>
         <v>-1</v>
       </c>
-      <c r="M59" s="60">
+      <c r="M59" s="97">
         <f>'月次推移'!L14-'月次推移'!L20</f>
         <v>-2</v>
       </c>
-      <c r="N59" s="61">
+      <c r="N59" s="98">
         <f>'月次推移'!M14-'月次推移'!M20</f>
         <v>-3</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="62" t="inlineStr">
+      <c r="B61" s="99" t="inlineStr">
         <is>
           <t>※ 数値はいずれも「月次推移」シートを参照。単位は名、マイナスは「▲」（赤字）で表示。</t>
         </is>
